--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\SoCDTtiNTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-calibration\InputData\trans\SoCDTtiNTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B539881-35F2-4ACF-93AE-EB11A251A4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42CAD3C-1921-4FBF-9916-C63629BB0C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10008" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="SoCDTtiNTY-psgr" sheetId="2" r:id="rId2"/>
-    <sheet name="SoCDTtiNTY-frgt" sheetId="4" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="5" r:id="rId2"/>
+    <sheet name="SoCDTtiNTY-psgr" sheetId="2" r:id="rId3"/>
+    <sheet name="SoCDTtiNTY-frgt" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="45">
   <si>
     <t>SoCDTtiNTY Share of Cargo Dist Transported that is New This Year</t>
   </si>
@@ -111,6 +112,63 @@
   </si>
   <si>
     <t>hydrogen vehicle</t>
+  </si>
+  <si>
+    <t>Calibrated share of cargo distance that is new this year (SoCDTtiNTY), by vehicle type and cargo type</t>
+  </si>
+  <si>
+    <t>Solved offline by calibration/steps/01-trans-turnover/solve.py (pinned mode) from the BAU export, confirmed by a headless run. The share is the one value at which retirements at the handoff year (IT + lifetime) equal New Vehicles in the start year, so 'Retiring Vehicles Summed Across Technologies' has no step; ANVCV (trans/ANVCV) then carries total sales onto the benchmark path every year. The same share applies to every vehicle technology in a row.</t>
+  </si>
+  <si>
+    <t>Vehicle type</t>
+  </si>
+  <si>
+    <t>Cargo type</t>
+  </si>
+  <si>
+    <t>Pre-calibration share</t>
+  </si>
+  <si>
+    <t>CALIBRATED SHARE USED IN THE OUTPUT TABS</t>
+  </si>
+  <si>
+    <t>Vehicle lifetime (yr)</t>
+  </si>
+  <si>
+    <t>Handoff year (IT + lifetime)</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>passenger</t>
+  </si>
+  <si>
+    <t>pinned mode: sales = benchmark path every year; ANVCV carries the difference; early retirements 16.38M vs smoothed real cohort 12.63M</t>
+  </si>
+  <si>
+    <t>NO SALES HISTORY -&gt; step-free criterion only; prompt the user to research a source</t>
+  </si>
+  <si>
+    <t>freight</t>
+  </si>
+  <si>
+    <t>pinned mode: sales = benchmark path every year; ANVCV carries the difference; early retirements 1.73M vs smoothed real cohort 1.43M</t>
+  </si>
+  <si>
+    <t>no modelled additions at IT - group skipped</t>
+  </si>
+  <si>
+    <t>Calibration record (2026-09-22)</t>
+  </si>
+  <si>
+    <t>Values now come from the Calibration tab, written by calibration/steps/01-trans-turnover/solve.py (pinned mode)</t>
+  </si>
+  <si>
+    <t>on the BAU export and confirmed by a headless run: retirement step at every handoff 0.0%.</t>
+  </si>
+  <si>
+    <t>SoCDTtiNTY and trans/ANVCV are solved together; see the ANVCV workbook and calibration/calibration-log.md.</t>
   </si>
 </sst>
 </file>
@@ -470,15 +528,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -486,49 +544,69 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -537,204 +615,321 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8628EAA0-6CDA-46A4-9551-1AF30E0810B8}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+    <col min="1" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="90.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5">
+        <v>5.8823528999999999E-2</v>
+      </c>
+      <c r="D5">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E5">
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>2042</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6">
+        <v>0.09</v>
+      </c>
+      <c r="D6">
+        <v>8.0861165190000001E-2</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>2037</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="D7">
+        <v>4.1162105259999998E-2</v>
+      </c>
+      <c r="E7">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>2049</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D8">
+        <v>2.9358024690000002E-2</v>
+      </c>
+      <c r="E8">
+        <v>34</v>
+      </c>
+      <c r="F8">
+        <v>2059</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="D9">
+        <v>3.0532475449999999E-2</v>
+      </c>
+      <c r="E9">
+        <v>33</v>
+      </c>
+      <c r="F9">
+        <v>2058</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="D10">
+        <v>5.8824040799999998E-2</v>
+      </c>
+      <c r="E10">
+        <v>17</v>
+      </c>
+      <c r="F10">
+        <v>2042</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11">
+        <v>5.8823528999999999E-2</v>
+      </c>
+      <c r="D11">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E11">
+        <v>15</v>
+      </c>
+      <c r="F11">
+        <v>2040</v>
+      </c>
+      <c r="G11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12">
+        <v>5.2631578999999998E-2</v>
+      </c>
+      <c r="D12">
+        <v>4.8805332860000002E-2</v>
+      </c>
+      <c r="E12">
         <v>20</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="F12">
+        <v>2045</v>
+      </c>
+      <c r="G12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="D13">
+        <v>4.0444444439999998E-2</v>
+      </c>
+      <c r="E13">
         <v>24</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2">
-        <f>1/17</f>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="C2">
-        <f t="shared" ref="C2:H2" si="0">1/17</f>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="D2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="E2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="F2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="G2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="H2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3">
-        <v>0.09</v>
-      </c>
-      <c r="C3">
-        <v>0.09</v>
-      </c>
-      <c r="D3">
-        <v>0.09</v>
-      </c>
-      <c r="E3">
-        <v>0.09</v>
-      </c>
-      <c r="F3">
-        <v>0.09</v>
-      </c>
-      <c r="G3">
-        <v>0.09</v>
-      </c>
-      <c r="H3">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>4.1599999999999998E-2</v>
-      </c>
-      <c r="C4">
-        <v>4.1599999999999998E-2</v>
-      </c>
-      <c r="D4">
-        <v>4.1599999999999998E-2</v>
-      </c>
-      <c r="E4">
-        <v>4.1599999999999998E-2</v>
-      </c>
-      <c r="F4">
-        <v>4.1599999999999998E-2</v>
-      </c>
-      <c r="G4">
-        <v>4.1599999999999998E-2</v>
-      </c>
-      <c r="H4">
-        <v>4.1599999999999998E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="F13">
+        <v>2049</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B5">
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="C5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="D5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="E5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="F5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="G5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="H5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D14">
+        <v>2.8760989010000002E-2</v>
+      </c>
+      <c r="E14">
+        <v>34</v>
+      </c>
+      <c r="F14">
+        <v>2059</v>
+      </c>
+      <c r="G14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B6">
-        <v>2.9819999999999999E-2</v>
-      </c>
-      <c r="C6">
-        <v>2.9819999999999999E-2</v>
-      </c>
-      <c r="D6">
-        <v>2.9819999999999999E-2</v>
-      </c>
-      <c r="E6">
-        <v>2.9819999999999999E-2</v>
-      </c>
-      <c r="F6">
-        <v>2.9819999999999999E-2</v>
-      </c>
-      <c r="G6">
-        <v>2.9819999999999999E-2</v>
-      </c>
-      <c r="H6">
-        <v>2.9819999999999999E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="D15">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="E15">
+        <v>33</v>
+      </c>
+      <c r="F15">
+        <v>2058</v>
+      </c>
+      <c r="G15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B7">
-        <v>5.8500000000000003E-2</v>
-      </c>
-      <c r="C7">
-        <v>5.8500000000000003E-2</v>
-      </c>
-      <c r="D7">
-        <v>5.8500000000000003E-2</v>
-      </c>
-      <c r="E7">
-        <v>5.8500000000000003E-2</v>
-      </c>
-      <c r="F7">
-        <v>5.8500000000000003E-2</v>
-      </c>
-      <c r="G7">
-        <v>5.8500000000000003E-2</v>
-      </c>
-      <c r="H7">
-        <v>5.8500000000000003E-2</v>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>17</v>
+      </c>
+      <c r="F16">
+        <v>2042</v>
+      </c>
+      <c r="G16" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -743,18 +938,259 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.109375" customWidth="1"/>
+    <col min="2" max="8" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <f>Calibration!$D$5</f>
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="C2">
+        <f>Calibration!$D$5</f>
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="D2">
+        <f>Calibration!$D$5</f>
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E2">
+        <f>Calibration!$D$5</f>
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="F2">
+        <f>Calibration!$D$5</f>
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="G2">
+        <f>Calibration!$D$5</f>
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="H2">
+        <f>Calibration!$D$5</f>
+        <v>5.2610446429999999E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <f>Calibration!$D$6</f>
+        <v>8.0861165190000001E-2</v>
+      </c>
+      <c r="C3">
+        <f>Calibration!$D$6</f>
+        <v>8.0861165190000001E-2</v>
+      </c>
+      <c r="D3">
+        <f>Calibration!$D$6</f>
+        <v>8.0861165190000001E-2</v>
+      </c>
+      <c r="E3">
+        <f>Calibration!$D$6</f>
+        <v>8.0861165190000001E-2</v>
+      </c>
+      <c r="F3">
+        <f>Calibration!$D$6</f>
+        <v>8.0861165190000001E-2</v>
+      </c>
+      <c r="G3">
+        <f>Calibration!$D$6</f>
+        <v>8.0861165190000001E-2</v>
+      </c>
+      <c r="H3">
+        <f>Calibration!$D$6</f>
+        <v>8.0861165190000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <f>Calibration!$D$7</f>
+        <v>4.1162105259999998E-2</v>
+      </c>
+      <c r="C4">
+        <f>Calibration!$D$7</f>
+        <v>4.1162105259999998E-2</v>
+      </c>
+      <c r="D4">
+        <f>Calibration!$D$7</f>
+        <v>4.1162105259999998E-2</v>
+      </c>
+      <c r="E4">
+        <f>Calibration!$D$7</f>
+        <v>4.1162105259999998E-2</v>
+      </c>
+      <c r="F4">
+        <f>Calibration!$D$7</f>
+        <v>4.1162105259999998E-2</v>
+      </c>
+      <c r="G4">
+        <f>Calibration!$D$7</f>
+        <v>4.1162105259999998E-2</v>
+      </c>
+      <c r="H4">
+        <f>Calibration!$D$7</f>
+        <v>4.1162105259999998E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <f>Calibration!$D$8</f>
+        <v>2.9358024690000002E-2</v>
+      </c>
+      <c r="C5">
+        <f>Calibration!$D$8</f>
+        <v>2.9358024690000002E-2</v>
+      </c>
+      <c r="D5">
+        <f>Calibration!$D$8</f>
+        <v>2.9358024690000002E-2</v>
+      </c>
+      <c r="E5">
+        <f>Calibration!$D$8</f>
+        <v>2.9358024690000002E-2</v>
+      </c>
+      <c r="F5">
+        <f>Calibration!$D$8</f>
+        <v>2.9358024690000002E-2</v>
+      </c>
+      <c r="G5">
+        <f>Calibration!$D$8</f>
+        <v>2.9358024690000002E-2</v>
+      </c>
+      <c r="H5">
+        <f>Calibration!$D$8</f>
+        <v>2.9358024690000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <f>Calibration!$D$9</f>
+        <v>3.0532475449999999E-2</v>
+      </c>
+      <c r="C6">
+        <f>Calibration!$D$9</f>
+        <v>3.0532475449999999E-2</v>
+      </c>
+      <c r="D6">
+        <f>Calibration!$D$9</f>
+        <v>3.0532475449999999E-2</v>
+      </c>
+      <c r="E6">
+        <f>Calibration!$D$9</f>
+        <v>3.0532475449999999E-2</v>
+      </c>
+      <c r="F6">
+        <f>Calibration!$D$9</f>
+        <v>3.0532475449999999E-2</v>
+      </c>
+      <c r="G6">
+        <f>Calibration!$D$9</f>
+        <v>3.0532475449999999E-2</v>
+      </c>
+      <c r="H6">
+        <f>Calibration!$D$9</f>
+        <v>3.0532475449999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <f>Calibration!$D$10</f>
+        <v>5.8824040799999998E-2</v>
+      </c>
+      <c r="C7">
+        <f>Calibration!$D$10</f>
+        <v>5.8824040799999998E-2</v>
+      </c>
+      <c r="D7">
+        <f>Calibration!$D$10</f>
+        <v>5.8824040799999998E-2</v>
+      </c>
+      <c r="E7">
+        <f>Calibration!$D$10</f>
+        <v>5.8824040799999998E-2</v>
+      </c>
+      <c r="F7">
+        <f>Calibration!$D$10</f>
+        <v>5.8824040799999998E-2</v>
+      </c>
+      <c r="G7">
+        <f>Calibration!$D$10</f>
+        <v>5.8824040799999998E-2</v>
+      </c>
+      <c r="H7">
+        <f>Calibration!$D$10</f>
+        <v>5.8824040799999998E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" customWidth="1"/>
+    <col min="2" max="8" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -780,173 +1216,201 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
-        <f>1/17</f>
-        <v>5.8823529411764705E-2</v>
+        <f>Calibration!$D$11</f>
+        <v>6.6346126409999998E-2</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:H2" si="0">1/17</f>
-        <v>5.8823529411764705E-2</v>
+        <f>Calibration!$D$11</f>
+        <v>6.6346126409999998E-2</v>
       </c>
       <c r="D2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>Calibration!$D$11</f>
+        <v>6.6346126409999998E-2</v>
       </c>
       <c r="E2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>Calibration!$D$11</f>
+        <v>6.6346126409999998E-2</v>
       </c>
       <c r="F2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>Calibration!$D$11</f>
+        <v>6.6346126409999998E-2</v>
       </c>
       <c r="G2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
+        <f>Calibration!$D$11</f>
+        <v>6.6346126409999998E-2</v>
       </c>
       <c r="H2">
-        <f t="shared" si="0"/>
-        <v>5.8823529411764705E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>Calibration!$D$11</f>
+        <v>6.6346126409999998E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
-        <f>1/19</f>
-        <v>5.2631578947368418E-2</v>
+        <f>Calibration!$D$12</f>
+        <v>4.8805332860000002E-2</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:H3" si="1">1/19</f>
-        <v>5.2631578947368418E-2</v>
+        <f>Calibration!$D$12</f>
+        <v>4.8805332860000002E-2</v>
       </c>
       <c r="D3">
-        <f t="shared" si="1"/>
-        <v>5.2631578947368418E-2</v>
+        <f>Calibration!$D$12</f>
+        <v>4.8805332860000002E-2</v>
       </c>
       <c r="E3">
-        <f t="shared" si="1"/>
-        <v>5.2631578947368418E-2</v>
+        <f>Calibration!$D$12</f>
+        <v>4.8805332860000002E-2</v>
       </c>
       <c r="F3">
-        <f t="shared" si="1"/>
-        <v>5.2631578947368418E-2</v>
+        <f>Calibration!$D$12</f>
+        <v>4.8805332860000002E-2</v>
       </c>
       <c r="G3">
-        <f t="shared" si="1"/>
-        <v>5.2631578947368418E-2</v>
+        <f>Calibration!$D$12</f>
+        <v>4.8805332860000002E-2</v>
       </c>
       <c r="H3">
-        <f t="shared" si="1"/>
-        <v>5.2631578947368418E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>Calibration!$D$12</f>
+        <v>4.8805332860000002E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4">
-        <v>2.8000000000000001E-2</v>
+        <f>Calibration!$D$13</f>
+        <v>4.0444444439999998E-2</v>
       </c>
       <c r="C4">
-        <v>2.8000000000000001E-2</v>
+        <f>Calibration!$D$13</f>
+        <v>4.0444444439999998E-2</v>
       </c>
       <c r="D4">
-        <v>2.8000000000000001E-2</v>
+        <f>Calibration!$D$13</f>
+        <v>4.0444444439999998E-2</v>
       </c>
       <c r="E4">
-        <v>2.8000000000000001E-2</v>
+        <f>Calibration!$D$13</f>
+        <v>4.0444444439999998E-2</v>
       </c>
       <c r="F4">
-        <v>2.8000000000000001E-2</v>
+        <f>Calibration!$D$13</f>
+        <v>4.0444444439999998E-2</v>
       </c>
       <c r="G4">
-        <v>2.8000000000000001E-2</v>
+        <f>Calibration!$D$13</f>
+        <v>4.0444444439999998E-2</v>
       </c>
       <c r="H4">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>Calibration!$D$13</f>
+        <v>4.0444444439999998E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5">
-        <v>2.9000000000000001E-2</v>
+        <f>Calibration!$D$14</f>
+        <v>2.8760989010000002E-2</v>
       </c>
       <c r="C5">
-        <v>2.9000000000000001E-2</v>
+        <f>Calibration!$D$14</f>
+        <v>2.8760989010000002E-2</v>
       </c>
       <c r="D5">
-        <v>2.9000000000000001E-2</v>
+        <f>Calibration!$D$14</f>
+        <v>2.8760989010000002E-2</v>
       </c>
       <c r="E5">
-        <v>2.9000000000000001E-2</v>
+        <f>Calibration!$D$14</f>
+        <v>2.8760989010000002E-2</v>
       </c>
       <c r="F5">
-        <v>2.9000000000000001E-2</v>
+        <f>Calibration!$D$14</f>
+        <v>2.8760989010000002E-2</v>
       </c>
       <c r="G5">
-        <v>2.9000000000000001E-2</v>
+        <f>Calibration!$D$14</f>
+        <v>2.8760989010000002E-2</v>
       </c>
       <c r="H5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>Calibration!$D$14</f>
+        <v>2.8760989010000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6">
+        <f>Calibration!$D$15</f>
         <v>3.0300000000000001E-2</v>
       </c>
       <c r="C6">
+        <f>Calibration!$D$15</f>
         <v>3.0300000000000001E-2</v>
       </c>
       <c r="D6">
+        <f>Calibration!$D$15</f>
         <v>3.0300000000000001E-2</v>
       </c>
       <c r="E6">
+        <f>Calibration!$D$15</f>
         <v>3.0300000000000001E-2</v>
       </c>
       <c r="F6">
+        <f>Calibration!$D$15</f>
         <v>3.0300000000000001E-2</v>
       </c>
       <c r="G6">
+        <f>Calibration!$D$15</f>
         <v>3.0300000000000001E-2</v>
       </c>
       <c r="H6">
+        <f>Calibration!$D$15</f>
         <v>3.0300000000000001E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
       <c r="B7">
+        <f>Calibration!$D$16</f>
         <v>0</v>
       </c>
       <c r="C7">
+        <f>Calibration!$D$16</f>
         <v>0</v>
       </c>
       <c r="D7">
+        <f>Calibration!$D$16</f>
         <v>0</v>
       </c>
       <c r="E7">
+        <f>Calibration!$D$16</f>
         <v>0</v>
       </c>
       <c r="F7">
+        <f>Calibration!$D$16</f>
         <v>0</v>
       </c>
       <c r="G7">
+        <f>Calibration!$D$16</f>
         <v>0</v>
       </c>
       <c r="H7">
+        <f>Calibration!$D$16</f>
         <v>0</v>
       </c>
     </row>
